--- a/_files/teste_projecao_gastos.xlsx
+++ b/_files/teste_projecao_gastos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBE7269-1E52-4045-A838-E1BC5284FDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7482D008-5EAA-497E-B250-A483979C8878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{093689EF-D701-4890-B8A9-8BD8B50DC7E2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{093689EF-D701-4890-B8A9-8BD8B50DC7E2}"/>
   </bookViews>
   <sheets>
     <sheet name="DADOS" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="99">
   <si>
     <t xml:space="preserve">SETOR </t>
   </si>
@@ -342,6 +342,15 @@
   <si>
     <t>Soma de VALOR TOTAL</t>
   </si>
+  <si>
+    <t>TIPO DE SOLICITAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVIÇO </t>
+  </si>
+  <si>
+    <t>MATERIAL</t>
+  </si>
 </sst>
 </file>
 
@@ -430,7 +439,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -477,12 +486,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -541,17 +563,22 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="13">
     <dxf>
       <border>
         <vertical style="thin">
@@ -634,9 +661,6 @@
       <numFmt numFmtId="165" formatCode="[$R$-416]\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -673,151 +697,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1892,16 +1771,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1916,7 +1795,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
+          <a:off x="7229475" y="3009900"/>
           <a:ext cx="10125075" cy="4029075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -14349,22 +14228,22 @@
     <dataField name="Soma de VALOR TOTAL" fld="5" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="13">
-    <format dxfId="13">
+    <format dxfId="12">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="11">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="9">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
     <format dxfId="6">
@@ -14743,7 +14622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18609D9C-E791-48E2-AC72-7D0345E1E97F}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="7" customWidth="1"/>
@@ -14753,7 +14632,8 @@
     <col min="5" max="5" width="17.28515625" style="7" customWidth="1"/>
     <col min="6" max="6" width="20.28515625" style="7" customWidth="1"/>
     <col min="7" max="7" width="22.42578125" style="7" customWidth="1"/>
-    <col min="8" max="9" width="9" style="2"/>
+    <col min="8" max="8" width="16.28515625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
@@ -14778,7 +14658,9 @@
       <c r="G1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="13"/>
+      <c r="H1" s="26" t="s">
+        <v>96</v>
+      </c>
       <c r="I1" s="13"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -14798,8 +14680,11 @@
       <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="27" t="s">
         <v>12</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -14819,8 +14704,11 @@
       <c r="F3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="27" t="s">
         <v>33</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -14840,7 +14728,10 @@
       <c r="F4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -14857,7 +14748,8 @@
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
@@ -14870,7 +14762,8 @@
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
@@ -14883,7 +14776,8 @@
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
@@ -14896,7 +14790,8 @@
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
@@ -14909,7 +14804,8 @@
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
@@ -14922,7 +14818,8 @@
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
@@ -14935,7 +14832,8 @@
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
@@ -14946,7 +14844,8 @@
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
@@ -14957,7 +14856,8 @@
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
@@ -14968,7 +14868,8 @@
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
@@ -14979,7 +14880,11 @@
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H16" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -15010,98 +14915,98 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="22"/>
-      <c r="C9" s="24" t="s">
+      <c r="C9" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" t="s">
         <v>95</v>
       </c>
       <c r="E9" s="22"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="22"/>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="25">
         <v>0</v>
       </c>
       <c r="E10" s="23"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="22"/>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="25">
         <v>59377.17</v>
       </c>
       <c r="E11" s="23"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="22"/>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="25">
         <v>170706</v>
       </c>
       <c r="E12" s="23"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="22"/>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="25">
         <v>154696</v>
       </c>
       <c r="E13" s="23"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="22"/>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="25">
         <v>270000</v>
       </c>
       <c r="E14" s="23"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="22"/>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="25">
         <v>34435.75</v>
       </c>
       <c r="E15" s="23"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="22"/>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="25">
         <v>39994.630000000005</v>
       </c>
       <c r="E16" s="23"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="22"/>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="D17" s="26"/>
+      <c r="D17" s="25"/>
       <c r="E17" s="23"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="22"/>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="25">
         <v>729209.54999999993</v>
       </c>
       <c r="E18" s="23"/>
@@ -15312,7 +15217,6 @@
         <v>242</v>
       </c>
       <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
       <c r="K3" s="6">
         <v>86826</v>
       </c>
@@ -27988,7 +27892,7 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2BCC596A-8F6E-4002-8EE0-4DEF79BC6697}">
           <x14:formula1>
             <xm:f>DADOS!$C$2:$C$5</xm:f>
@@ -28025,6 +27929,12 @@
           </x14:formula1>
           <xm:sqref>A2:A641</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CF7FD3E7-662A-4B2B-99C3-23126DE0A3C7}">
+          <x14:formula1>
+            <xm:f>DADOS!$H$2:$H$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J640</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
